--- a/extenbooks/S705_extenbook.xlsx
+++ b/extenbooks/S705_extenbook.xlsx
@@ -17795,7 +17795,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: ingested</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -19365,11 +19365,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19392,112 +19392,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Figure 7.15 — US Industry Average Rates of Profit, 1987–2005 (BEA/Shaikh 2008)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>chapter</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>extenbook_published</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>["3_research", "4_adequacy", "5_ingestion", "6_extension", "7_replication", "8_output"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{"research_json": "Technical/research/S705_research.json", "adequacy_report": "Technical/docs/chapters/CH7_ADEQUACY_REPORT.json", "dpr": "Technical/docs/series/S705_DPR.md", "epr": "Technical/docs/series/S705_EPR.md", "loader": "Technical/code/L01_loaders/L01_S705_load.py", "processor": "Technical/code/P02_processors/P02_S705_construct.py", "validator": "Technical/code/V03_validators/V03_S705_validate.py", "processed": "Technical/data/processed/S705.parquet", "chopped_csv": "Technical/chopped/S705.csv", "extenbook_xlsx": "Technical/extenbooks/S705_extenbook.xlsx"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>subseries_ids</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>["S705-A"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>subsource_ids</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>["SHAIKH_2008_APPENDIX_7_2_ROP"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>content_type</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>time_series</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>extension_status</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>feasible_deferred</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S705_extenbook.xlsx
+++ b/extenbooks/S705_extenbook.xlsx
@@ -17742,7 +17742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A163"/>
+  <dimension ref="A1:A204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -17881,7 +17881,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>**S705** is the **rate (decimal; ROP = (PG - DEP) / K(-1), aggregate-before-ratio across 30 retained industries)** for the period 1987–2005. It appears in Shaikh (2016) as Fig7.15. The series is a multi-industry panel published as part of Shaikh's Appendix 7.2 derived data (with underlying BEA / OECD primary inputs).</t>
+          <t>**S705** is the **rate (decimal; ROP = (PG - DEP) / K(-1), aggregate-before-ratio across 30 retained industries)** for the period 1987–2005. It appears in Shaikh (2016) as Fig7.15. The series is a multi-industry panel published as part of Shaikh's Appendix 7.2 derived data (with underlying BEA (US Bureau of Economic Analysis) / OECD primary inputs).</t>
         </is>
       </c>
     </row>
@@ -17935,7 +17935,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>| **S705-A** | 1987–2005 | Appendix 7.2 ropdataUSind, byte-exact transcription of Shaikh 2008 NAICS reconstruction | rate (decimal) | local salvaged xlsx + Wayback fallback (https://web.archive.org/web/2023/http://www.anwarshaikhecon.org/) |</t>
+          <t>| **S705-A** (subseries — one data line within S705) | 1987–2005 | Appendix 7.2 ropdataUSind, byte-exact transcription of Shaikh 2008 NAICS reconstruction | rate (decimal) | local salvaged xlsx + Wayback fallback (https://web.archive.org/web/2023/http://www.anwarshaikhecon.org/) |</t>
         </is>
       </c>
     </row>
@@ -17975,7 +17975,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1. The salvaged xlsx is the **byte-exact published series**; rebuilding from BEA would require re-applying WEQ/OOH/inventory/reserve adjustments at a specific 2008 NIPA vintage, which is not recoverable from current BEA endpoints.</t>
+          <t>1. The salvaged xlsx is the **byte-exact published series**; rebuilding from BEA would require re-applying WEQ (wage-equivalent) / OOH (owner-occupied-housing) / inventory / reserve adjustments at a specific 2008 NIPA (US National Income and Product Accounts) vintage, which is not recoverable from current BEA endpoints.</t>
         </is>
       </c>
     </row>
@@ -18131,7 +18131,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>- **CD2 legacy ID**: `S034`</t>
+          <t>- **CD2 legacy ID** (identifier in CD2, the predecessor build of this dataset): `S034`</t>
         </is>
       </c>
     </row>
@@ -18155,7 +18155,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>## 9. Validation expectation</t>
+          <t>## Notation (plain-language key)</t>
         </is>
       </c>
     </row>
@@ -18165,139 +18165,155 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
+          <t>Short forms used above, in plain language (this record is a downloadable external artifact):</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>- **S### / -A** — series identifiers in this project (e.g. S705); a trailing letter (e.g. S705-A) marks a *subseries* — one data line within that series.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>- **DPR / EPR** — Data Provenance Record (this file) / Extension Provenance Record (its companion).</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>- **Phase N** — Anu Framework pipeline stages: Phase 4 = adequacy/readiness review, Phase 5 = ingestion, Phase 6 = extension, Phase 9 = visualization.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>- **L01 / P02 / V03** — the per-series load / process / validate scripts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>- **CD2** — the predecessor build of this dataset.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>- **ROP** — (average) rate of profit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>- **IROP** — incremental rate of profit: the return on newly added capital (the year-to-year change in profit divided by the new investment that produced it).</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>- **BEA** — US Bureau of Economic Analysis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>- **NIPA** — US National Income and Product Accounts (published by the BEA).</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>- **NAICS** — North American Industry Classification System.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>- **WEQ** — wage equivalent: an imputed labour income for self-employed / proprietors, adjusted out of surplus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>- **OOH** — owner-occupied housing: an adjustment removing imputed housing income.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>- **GOS** — Gross Operating Surplus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>- **FRB Z.1** — Federal Reserve Board Z.1 (Financial Accounts of the United States).</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>- **MAE** — mean absolute error.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>## 9. Validation expectation</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
           <t>- **Tolerance**: ±1.0% per year (time_series; tightened to ~0.0% in practice because we read the xlsx byte-exact).</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
+    <row r="96">
+      <c r="A96" t="inlineStr">
         <is>
           <t>- **Expected MAE** against the salvaged xlsx column: ~0 (verbatim re-read).</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="4">
+    <row r="99">
+      <c r="A99" s="4">
         <f>== EPR: S705_EPR.md ===</f>
         <v/>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t># S705 — Extension Provenance Record</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr"/>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>**Series**: S705 — Figure 7.15 — US Industry Average Rates of Profit, 1987–2005 (BEA/Shaikh 2008)</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>**Phase**: 6 (Extension)</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>**Construction classification**: `composite`</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>**Extension method**: Phase 5 = **direct byte-exact replication** from Shaikh Appendix 7.2 (salvaged xlsx). Extension to current year = **end-to-end BEA / OECD primary re-fetch** (deferred per Phase 4 adequacy)</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>**Authored**: 2026-05-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>**Author**: opus-subagent-ch7-fanout</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>**Related**: `S705_DPR.md`</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>## 1. Why this series is extendable in principle</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>`content_type = time_series` and the underlying primaries (BEA GDP-by-Industry; BEA Fixed Assets; OECD STAN; FRB Z.1) are continuously published. The Phase 4 adequacy confirmed all primary endpoints return HTTP 200.</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>## 2. Construction classification</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>`composite`. Per the Anu rule on lazy splices:</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr"/>
-    </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>&gt; "If the original computed a formula (P*=D/(r-g), r=NOS/K, ratio=X/Y), the extension must compute the same formula with extended component data."</t>
+          <t># S705 — Extension Provenance Record</t>
         </is>
       </c>
     </row>
@@ -18307,51 +18323,59 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>This applies here. The series is **not** a directly-observed time series — it is computed from multiple BEA / OECD components with non-trivial methodological adjustments (WEQ removal, OOH removal, inventory/reserve additions, exclusion-list restriction, aggregate-before-ratio). Therefore extension to 2024 cannot be a growth-rate splice on the published value; it must **re-fetch the components** and **re-compute the formula**.</t>
+          <t>**Series**: S705 — Figure 7.15 — US Industry Average Rates of Profit, 1987–2005 (BEA/Shaikh 2008)</t>
         </is>
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr"/>
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>**Phase**: 6 (Extension)</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>## 3. Method</t>
+          <t>**Construction classification**: `composite`</t>
         </is>
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr"/>
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>**Extension method**: Phase 5 = **direct byte-exact replication** from Shaikh Appendix 7.2 (salvaged xlsx). Extension to current year = **end-to-end BEA / OECD primary re-fetch** (deferred per Phase 4 adequacy)</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>### 3.1 Phase 5 byte-exact replication (this wave)</t>
+          <t>**Authored**: 2026-05-18</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr"/>
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>**Author**: opus-subagent-ch7-fanout</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>```</t>
+          <t>**Related**: `S705_DPR.md`</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>INPUTS</t>
-        </is>
-      </c>
+      <c r="A109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Shaikh Appendix 7.2 xlsx in SalvagedInputs/book_data/ShaikhChoppedTables/</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -18361,172 +18385,156 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>PROCEDURE</t>
+          <t>## 1. Why this series is extendable in principle</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  L01: read xlsx with header at row 1 (descriptive title at row 0)</t>
-        </is>
-      </c>
+      <c r="A113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">  L01: write one raw parquet per industry column (long form: year, value, subseries_id, source_id, units)</t>
+          <t>`content_type = time_series` and the underlying primaries (BEA (US Bureau of Economic Analysis) GDP-by-Industry; BEA Fixed Assets; OECD STAN (Structural Analysis database); FRB Z.1 (Federal Reserve Board Z.1, Financial Accounts of the United States)) are continuously published. The Phase 4 adequacy confirmed all primary endpoints return HTTP 200.</t>
         </is>
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  P02: union the raw parquets, sort by year + subseries_id, emit data/processed/S705.parquet</t>
-        </is>
-      </c>
+      <c r="A115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">  V03: compare row-by-row vs xlsx; expect MAE ≈ 0</t>
+          <t>## 2. Construction classification</t>
         </is>
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>```</t>
-        </is>
-      </c>
+      <c r="A117" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr"/>
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>`composite`. Per the Anu rule on lazy splices:</t>
+        </is>
+      </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>### 3.2 Phase 6 extension (deferred)</t>
-        </is>
-      </c>
+      <c r="A119" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr"/>
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>&gt; "If the original computed a formula (P*=D/(r-g), r=NOS/K, ratio=X/Y), the extension must compute the same formula with extended component data."</t>
+        </is>
+      </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>```</t>
-        </is>
-      </c>
+      <c r="A121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>INPUTS (deferred wave)</t>
+          <t>This applies here. The series is **not** a directly-observed time series — it is computed from multiple BEA / OECD components with non-trivial methodological adjustments (WEQ (wage-equivalent) removal, OOH (owner-occupied-housing) removal, inventory/reserve additions, exclusion-list restriction, aggregate-before-ratio). Therefore extension to 2024 cannot be a growth-rate splice on the published value; it must **re-fetch the components** and **re-compute the formula**.</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  BEA GDPbyInd_VA_NAICS via BEA API (apps.bea.gov; current vintage)</t>
-        </is>
-      </c>
+      <c r="A123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">  BEA Fixed Asset Tables 3.1ES / 3.4ES / 3.7ES via BEA API</t>
+          <t>## 3. Method</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  NIPA Table 7.12 for OOH lines</t>
-        </is>
-      </c>
+      <c r="A125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">  FRB Z.1 release for L.109 / L.114–117 reserve flows</t>
+          <t>### 3.1 Phase 5 byte-exact replication (this wave)</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Shaikh_2008_Appendix_B_industries.csv for the 31-industry drop key</t>
-        </is>
-      </c>
+      <c r="A127" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr"/>
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>The scripts named below are the per-series loader (`L01`), processor (`P02`), and validator (`V03`).</t>
+        </is>
+      </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>PROCEDURE</t>
-        </is>
-      </c>
+      <c r="A129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">  L01_ext: fetch above (cache 30 days)</t>
+          <t>```</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">  P02_ext: re-apply WEQ/OOH/inventory/reserve, EXCLUDING post-2013 R&amp;D/IP capitalization to preserve Shaikh's 2008 capital concept</t>
+          <t>INPUTS</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">  V03_ext: re-validate against book-period; overlap should match within 1.0%; extension years carry tolerance documentation</t>
+          <t xml:space="preserve">  Shaikh Appendix 7.2 xlsx in SalvagedInputs/book_data/ShaikhChoppedTables/</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>```</t>
-        </is>
-      </c>
+      <c r="A133" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr"/>
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>PROCEDURE</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Byte-exact 1987-2005 published in Phase 5 from salvaged xlsx. End-to-end BEA re-fetch + WEQ/OOH/inventory/reserve recomputation to extend through 2024 is feasible but requires careful exclusion of post-2013 R&amp;D/IP capitalization to preserve Shaikh's 2008 capital concept — deferred to a future wave that can ratify CD2's extension trajectory.</t>
+          <t xml:space="preserve">  L01: read xlsx with header at row 1 (descriptive title at row 0)</t>
         </is>
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr"/>
+      <c r="A136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  L01: write one raw parquet per industry column (long form: year, value, subseries_id, source_id, units)</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>## 4. Component re-fetching</t>
+          <t xml:space="preserve">  P02: union the raw parquets, sort by year + subseries_id, emit data/processed/S705.parquet</t>
         </is>
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr"/>
+      <c r="A138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  V03: compare row-by-row vs xlsx; expect MAE ≈ 0</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Required for any extension. The Anu rule explicitly forbids splicing a derived rate; we re-fetch and re-compute.</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -18536,7 +18544,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>## 5. Proxies</t>
+          <t>### 3.2 Phase 6 extension (deferred)</t>
         </is>
       </c>
     </row>
@@ -18546,37 +18554,49 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>**None.** Shaikh's Appendix 7.2 panel is itself derived from BEA primaries; the BEA primaries remain the canonical source. No substitution.</t>
+          <t>```</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr"/>
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>INPUTS (deferred wave)</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>## 6. Synthetic data</t>
+          <t xml:space="preserve">  BEA GDPbyInd_VA_NAICS via BEA API (apps.bea.gov; current vintage)</t>
         </is>
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr"/>
+      <c r="A146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  BEA Fixed Asset Tables 3.1ES / 3.4ES / 3.7ES via BEA API</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>**None.** No interpolation.</t>
+          <t xml:space="preserve">  NIPA Table 7.12 for OOH lines</t>
         </is>
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr"/>
+      <c r="A148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  FRB Z.1 release for L.109 / L.114–117 reserve flows</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>## 7. Failure modes &amp; graceful degradation</t>
+          <t xml:space="preserve">  Shaikh_2008_Appendix_B_industries.csv for the 31-industry drop key</t>
         </is>
       </c>
     </row>
@@ -18586,35 +18606,35 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>| Failure | Detection | Action |</t>
+          <t>PROCEDURE</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>|---|---|---|</t>
+          <t xml:space="preserve">  L01_ext: fetch above (cache 30 days)</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>| Salvaged xlsx missing | L01 file-exists check | FAIL (re-fetch from Wayback snapshot) |</t>
+          <t xml:space="preserve">  P02_ext: re-apply WEQ/OOH/inventory/reserve, EXCLUDING post-2013 R&amp;D/IP capitalization to preserve Shaikh's 2008 capital concept</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>| Excluded industry not present in panel | P02 schema check | log warning; emit panel-as-is |</t>
+          <t xml:space="preserve">  V03_ext: re-validate against book-period; overlap should match within 1.0%; extension years carry tolerance documentation</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>| BEA endpoint 4xx/5xx (extension only) | L01_ext fetcher | retry 3× w/ 2s backoff; degrade extension |</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -18624,7 +18644,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>## 8. Splice diagnostics (reported by V03)</t>
+          <t>Byte-exact 1987-2005 published in Phase 5 from salvaged xlsx. End-to-end BEA re-fetch + WEQ/OOH/inventory/reserve recomputation to extend through 2024 is feasible but requires careful exclusion of post-2013 R&amp;D/IP capitalization to preserve Shaikh's 2008 capital concept — deferred to a future wave that can ratify CD2's extension trajectory.</t>
         </is>
       </c>
     </row>
@@ -18634,7 +18654,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>V03 emits MAE, max absolute error, and a divergence list of any year where the byte-exact reproduction differs from the xlsx column by &gt; {tol}%. For S705/S706/S709/S710/S711, that tolerance is **1.0%** (time_series default); in practice MAE ≈ 0 because the L01 reads the xlsx directly.</t>
+          <t>## 4. Component re-fetching</t>
         </is>
       </c>
     </row>
@@ -18644,7 +18664,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>## 9. CD2 divergence pre-disclosure</t>
+          <t>Required for any extension. The Anu rule explicitly forbids splicing a derived rate; we re-fetch and re-compute.</t>
         </is>
       </c>
     </row>
@@ -18654,7 +18674,246 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>CD2's per-series CSV for `S034` is the closest legacy comparison. CD2 used the same Shaikh Appendix 7.2 source for the book period and applied its own end-to-end re-run for the 2006–2024 extension. RSCD's Phase 5 deliverable does not extend; in this wave RSCD's book-period values should agree with CD2 at MAE = 0 (modulo presentation choices on the All-Private aggregate column).</t>
+          <t>## 5. Proxies</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>**None.** Shaikh's Appendix 7.2 panel is itself derived from BEA primaries; the BEA primaries remain the canonical source. No substitution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>## 6. Synthetic data</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>**None.** No interpolation.</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>## 7. Failure modes &amp; graceful degradation</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>| Failure | Detection | Action |</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>|---|---|---|</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>| Salvaged xlsx missing | L01 file-exists check | FAIL (re-fetch from Wayback snapshot) |</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>| Excluded industry not present in panel | P02 schema check | log warning; emit panel-as-is |</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>| BEA endpoint 4xx/5xx (extension only) | L01_ext fetcher | retry 3× w/ 2s backoff; degrade extension |</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>## 8. Splice diagnostics (reported by V03)</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>V03 emits MAE, max absolute error, and a divergence list of any year where the byte-exact reproduction differs from the xlsx column by &gt; {tol}%. For S705/S706/S709/S710/S711, that tolerance is **1.0%** (time_series default); in practice MAE ≈ 0 because the L01 reads the xlsx directly.</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>## 9. CD2 divergence pre-disclosure</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>CD2 (the predecessor build of this dataset) has a per-series CSV for `S034` that is the closest legacy comparison. CD2 used the same Shaikh Appendix 7.2 source for the book period and applied its own end-to-end re-run for the 2006–2024 extension. RSCD's Phase 5 deliverable does not extend; in this wave RSCD's book-period values should agree with CD2 at MAE = 0 (modulo presentation choices on the All-Private aggregate column).</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>## Notation (plain-language key)</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Short forms used above, in plain language (this record is a downloadable external artifact):</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>- **S### / -A** — series identifiers in this project (e.g. S705); a trailing letter (e.g. S705-A) marks a *subseries* — one data line within that series.</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>- **DPR / EPR** — Data Provenance Record / Extension Provenance Record (this file).</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>- **Phase N** — Anu Framework pipeline stages: Phase 4 = adequacy/readiness review, Phase 5 = ingestion, Phase 6 = extension.</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>- **L01 / P02 / V03** — the per-series load / process / validate scripts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>- **CD2** — the predecessor build of this dataset.</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>- **ROP** — (average) rate of profit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>- **BEA** — US Bureau of Economic Analysis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>- **NIPA** — US National Income and Product Accounts (published by the BEA).</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>- **NAICS** — North American Industry Classification System.</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>- **STAN** — OECD Structural Analysis database.</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>- **WEQ** — wage equivalent: an imputed labour income for self-employed / proprietors, adjusted out of surplus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>- **OOH** — owner-occupied housing: an adjustment removing imputed housing income.</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>- **FRB Z.1** — Federal Reserve Board Z.1 (Financial Accounts of the United States).</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>- **MAE** — mean absolute error.</t>
         </is>
       </c>
     </row>
@@ -19350,7 +19609,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-05-18T22:08:08.249736+00:00</t>
+          <t>2026-07-02T06:25:12.218869+00:00</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S705_extenbook.xlsx
+++ b/extenbooks/S705_extenbook.xlsx
@@ -19609,7 +19609,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-07-02T06:25:12.218869+00:00</t>
+          <t>2026-07-11T03:44:25.967474+00:00</t>
         </is>
       </c>
     </row>
@@ -19624,11 +19624,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
-    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -19651,6 +19651,150 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>primary_source</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>SHAIKH_2008_APPENDIX_7_2_ROP</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>construction</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>composite</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>book_period_validated</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>validation_class</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pipeline_consistent</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>triage</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>{"verdict": "publish", "reason": "Reconstructed multi-industry panel (30 industries + All-Private) from Shaikh's online Appendix 7.2 (BEA NIPA, with WEQ / owner-occupied-housing / inventory-reserve adjustments). Figure 7.15, period, and source ('Shaikh 2008') verified against KB ch07; all four book_quotes verbatim-confirmed. reference_values are round-trip-circular against the salvaged appendix (auditability only) \u2014 the genuine book tie is the figure-overlay (MATCH per FIGURE_REPRO_ch07).", "date": "2026-06-11"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>dpr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S705_DPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>epr</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Technical/docs/series/S705_EPR.md</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>content_type</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>time_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>units</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>rate (decimal; ROP = (PG - DEP) / K(-1), aggregate-before-ratio across 30 retained industries)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>proxy</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>publish</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>chapter</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
